--- a/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
+++ b/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="681">
   <si>
     <t>韩国济州岛旅行 · 最终方案首页</t>
   </si>
@@ -36,7 +36,7 @@
     <t>网站只读取这一页作为最终攻略；后面的工作表都是候选资料和处理记录。</t>
   </si>
   <si>
-    <t>黄色单元格可直接修改；保存 Excel 后约 4 秒同步网站。当前已确定 14/18 项，待补充 4 项。</t>
+    <t>黄色单元格可直接修改；保存 Excel 后约 4 秒同步网站。当前已确定 15/18 项，待补充 3 项。</t>
   </si>
   <si>
     <t>一、基础信息  ·  网站顶部与旅行概览</t>
@@ -66,63 +66,63 @@
     <t>出行日期</t>
   </si>
   <si>
-    <t>待团队确认</t>
+    <t>2026年8月21日–23日（周五–周日）</t>
+  </si>
+  <si>
+    <t>确定日期后直接在黄色单元格修改</t>
+  </si>
+  <si>
+    <t>行程结构</t>
+  </si>
+  <si>
+    <t>3 天 2 晚 · 国际航班直达济州</t>
+  </si>
+  <si>
+    <t>例如：3 天 2 晚 · 国际航班直达济州</t>
+  </si>
+  <si>
+    <t>同行人数</t>
+  </si>
+  <si>
+    <t>用于住宿、餐饮和活动人数判断</t>
+  </si>
+  <si>
+    <t>住宿晚数</t>
+  </si>
+  <si>
+    <t>当前按 3 天 2 晚设计</t>
+  </si>
+  <si>
+    <t>人均预算</t>
+  </si>
+  <si>
+    <t>¥1,000–1,500 / 人（不含往返济州机票）</t>
+  </si>
+  <si>
+    <t>可填写数字或预算区间</t>
+  </si>
+  <si>
+    <t>方案说明</t>
+  </si>
+  <si>
+    <t>六人按真实消费重算：正餐约 ¥100/人，穿插民宿做饭与一起吃宵夜；岛内公交优先、必要时短途拼车，不默认全程打车或包车；贵景点可换成免费海岸、市场和步道。</t>
+  </si>
+  <si>
+    <t>网站首页的行程摘要</t>
+  </si>
+  <si>
+    <t>二、住宿确认  ·  民宿未确定前保持橙色“待补充”</t>
+  </si>
+  <si>
+    <t>民宿名称</t>
+  </si>
+  <si>
+    <t>待选择｜济州市区六人酒店或公寓</t>
   </si>
   <si>
     <t>待补充</t>
   </si>
   <si>
-    <t>确定日期后直接在黄色单元格修改</t>
-  </si>
-  <si>
-    <t>行程结构</t>
-  </si>
-  <si>
-    <t>3 天 2 晚 · 国际航班直达济州</t>
-  </si>
-  <si>
-    <t>例如：3 天 2 晚 · 国际航班直达济州</t>
-  </si>
-  <si>
-    <t>同行人数</t>
-  </si>
-  <si>
-    <t>用于住宿、餐饮和活动人数判断</t>
-  </si>
-  <si>
-    <t>住宿晚数</t>
-  </si>
-  <si>
-    <t>当前按 3 天 2 晚设计</t>
-  </si>
-  <si>
-    <t>人均预算</t>
-  </si>
-  <si>
-    <t>¥1,000–1,500 / 人（不含往返济州机票）</t>
-  </si>
-  <si>
-    <t>可填写数字或预算区间</t>
-  </si>
-  <si>
-    <t>方案说明</t>
-  </si>
-  <si>
-    <t>六人按真实消费重算：正餐约 ¥100/人，穿插民宿做饭与一起吃宵夜；岛内公交优先、必要时短途拼车，不默认全程打车或包车；贵景点可换成免费海岸、市场和步道。</t>
-  </si>
-  <si>
-    <t>网站首页的行程摘要</t>
-  </si>
-  <si>
-    <t>二、住宿确认  ·  民宿未确定前保持橙色“待补充”</t>
-  </si>
-  <si>
-    <t>民宿名称</t>
-  </si>
-  <si>
-    <t>待选择｜济州市区六人酒店或公寓</t>
-  </si>
-  <si>
     <t>确定住宿后填写真实名称</t>
   </si>
   <si>
@@ -579,7 +579,7 @@
     <t>reserve-dates-flight</t>
   </si>
   <si>
-    <t>确定日期与国际直达济州往返航班</t>
+    <t>预订国际直达济州往返航班</t>
   </si>
   <si>
     <t>机票</t>
@@ -591,7 +591,7 @@
     <t>待认领</t>
   </si>
   <si>
-    <t>优先完成</t>
+    <t>尽快确认</t>
   </si>
   <si>
     <t>不要购买经首尔转韩国国内线的方案；六人的去回航班与行李额需统一</t>
@@ -624,9 +624,6 @@
     <t>待补充真实链接</t>
   </si>
   <si>
-    <t>日期确认后立即</t>
-  </si>
-  <si>
     <t>比较房型、床型、含税总价、位置、取消政策和延迟入住限制</t>
   </si>
   <si>
@@ -921,6 +918,9 @@
     <t>请团队优先投递 3–5 个真实住宿链接</t>
   </si>
   <si>
+    <t>priceLabel</t>
+  </si>
+  <si>
     <t>文字</t>
   </si>
   <si>
@@ -2067,7 +2067,7 @@
     <t>当前重点</t>
   </si>
   <si>
-    <t>确定日期与直达航班、住宿、包车和具体餐厅</t>
+    <t>确定日期与直达航班、住宿、公交班次和具体餐厅</t>
   </si>
   <si>
     <t>可投递链接，也可直接写文字诉求</t>
@@ -2853,11 +2853,11 @@
         <v>12</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2869,17 +2869,17 @@
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6">
         <v>6</v>
@@ -2901,7 +2901,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6">
         <v>2</v>
@@ -2923,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -2935,17 +2935,17 @@
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -2957,17 +2957,17 @@
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2995,14 +2995,14 @@
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>31</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="9" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>34</v>
@@ -3198,7 +3198,7 @@
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="9" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>57</v>
@@ -3859,50 +3859,50 @@
         <v>186</v>
       </c>
       <c r="G47" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>198</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="48" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="14" t="s">
         <v>200</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>201</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D48" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>202</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>203</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>186</v>
       </c>
       <c r="G48" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H48" s="14" t="s">
         <v>204</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="49" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>209</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>197</v>
@@ -3911,24 +3911,24 @@
         <v>186</v>
       </c>
       <c r="G49" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="50" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="C50" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="D50" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>79</v>
@@ -3937,10 +3937,10 @@
         <v>186</v>
       </c>
       <c r="G50" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="H50" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4119,13 +4119,13 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>487</v>
@@ -4173,46 +4173,46 @@
         <v>509</v>
       </c>
       <c r="T3" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="U3" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>232</v>
       </c>
       <c r="V3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="W3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="AA3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="AB3" s="21" t="s">
+      <c r="AC3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AD3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AE3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AF3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AF3" s="21" t="s">
+      <c r="AG3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="AG3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AH3" s="21" t="s">
         <v>512</v>
@@ -4220,26 +4220,26 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>264</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>265</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G4" s="35"/>
       <c r="H4" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I4" s="32" t="s">
         <v>561</v>
@@ -4278,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="V4" s="24" t="s">
         <v>569</v>
@@ -4294,17 +4294,17 @@
       </c>
       <c r="Z4" s="24"/>
       <c r="AA4" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB4" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="AB4" s="24" t="s">
-        <v>258</v>
-      </c>
       <c r="AC4" s="24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AD4" s="24"/>
       <c r="AE4" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF4" s="24"/>
       <c r="AG4" s="24" t="s">
@@ -4322,13 +4322,13 @@
         <v>323</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>326</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>138</v>
@@ -4390,17 +4390,17 @@
       </c>
       <c r="Z5" s="14"/>
       <c r="AA5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB5" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="AB5" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="AC5" s="14" t="s">
         <v>330</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF5" s="14"/>
       <c r="AG5" s="14" t="s">
@@ -4424,7 +4424,7 @@
         <v>346</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F6" s="32" t="s">
         <v>579</v>
@@ -4486,17 +4486,17 @@
       </c>
       <c r="Z6" s="24"/>
       <c r="AA6" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB6" s="24" t="s">
         <v>257</v>
-      </c>
-      <c r="AB6" s="24" t="s">
-        <v>258</v>
       </c>
       <c r="AC6" s="24" t="s">
         <v>350</v>
       </c>
       <c r="AD6" s="24"/>
       <c r="AE6" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF6" s="24"/>
       <c r="AG6" s="24" t="s">
@@ -4514,7 +4514,7 @@
         <v>332</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>336</v>
@@ -4582,17 +4582,17 @@
       </c>
       <c r="Z7" s="14"/>
       <c r="AA7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB7" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="AB7" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="AC7" s="14" t="s">
         <v>340</v>
       </c>
       <c r="AD7" s="14"/>
       <c r="AE7" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AF7" s="14"/>
       <c r="AG7" s="14" t="s">
@@ -4643,7 +4643,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4703,10 +4703,10 @@
         <v>598</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>599</v>
@@ -4721,46 +4721,46 @@
         <v>382</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="L3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="N3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="O3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="P3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="R3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="S3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="T3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="U3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="V3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="W3" s="21" t="s">
         <v>512</v>
@@ -4768,19 +4768,19 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>249</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>250</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>601</v>
@@ -4811,17 +4811,17 @@
       </c>
       <c r="O4" s="24"/>
       <c r="P4" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q4" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="Q4" s="24" t="s">
+      <c r="R4" s="24" t="s">
         <v>258</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>259</v>
       </c>
       <c r="S4" s="24"/>
       <c r="T4" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U4" s="24"/>
       <c r="V4" s="24" t="s">
@@ -4839,13 +4839,13 @@
         <v>301</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>304</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>607</v>
@@ -4876,17 +4876,17 @@
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q5" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="R5" s="14" t="s">
         <v>308</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U5" s="14"/>
       <c r="V5" s="14" t="s">
@@ -4898,19 +4898,19 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="D6" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="32" t="s">
         <v>275</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>276</v>
       </c>
       <c r="F6" s="32" t="s">
         <v>415</v>
@@ -4941,17 +4941,17 @@
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q6" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="Q6" s="24" t="s">
-        <v>258</v>
-      </c>
       <c r="R6" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S6" s="24"/>
       <c r="T6" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U6" s="24"/>
       <c r="V6" s="24" t="s">
@@ -5103,7 +5103,7 @@
         <v>81</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>80</v>
@@ -5142,7 +5142,7 @@
         <v>90</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M5" s="14"/>
     </row>
@@ -5259,7 +5259,7 @@
         <v>116</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M8" s="24" t="s">
         <v>115</v>
@@ -5300,7 +5300,7 @@
         <v>126</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>125</v>
@@ -5571,7 +5571,7 @@
         <v>173</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>80</v>
@@ -5727,50 +5727,50 @@
         <v>186</v>
       </c>
       <c r="G6" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" s="24" t="s">
         <v>198</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>200</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>201</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D7" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>202</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>203</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>186</v>
       </c>
       <c r="G7" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H7" s="14" t="s">
         <v>204</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="C8" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="24" t="s">
         <v>208</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>209</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>197</v>
@@ -5779,24 +5779,24 @@
         <v>186</v>
       </c>
       <c r="G8" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="24" t="s">
         <v>210</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>79</v>
@@ -5805,10 +5805,10 @@
         <v>186</v>
       </c>
       <c r="G9" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5878,7 +5878,7 @@
         <v>631</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>632</v>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="24">
         <v>6</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="14">
         <v>2</v>
@@ -6050,7 +6050,7 @@
         <v>659</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>660</v>
@@ -6202,7 +6202,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6263,120 +6263,120 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="D3" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="F3" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="G3" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="H3" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="I3" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="J3" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="K3" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="L3" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="M3" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="N3" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="O3" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="P3" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="Q3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="R3" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="S3" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="T3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="U3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="U3" s="21" t="s">
+      <c r="V3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="W3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="X3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="C4" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="F4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="G4" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="H4" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="I4" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="J4" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="K4" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="L4" s="24" t="s">
         <v>254</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>255</v>
       </c>
       <c r="M4" s="26">
         <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O4" s="27">
         <v>5</v>
@@ -6391,17 +6391,17 @@
         <v>0</v>
       </c>
       <c r="S4" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T4" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="U4" s="28" t="s">
         <v>258</v>
-      </c>
-      <c r="U4" s="28" t="s">
-        <v>259</v>
       </c>
       <c r="V4" s="24"/>
       <c r="W4" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X4" s="24"/>
       <c r="Y4" s="24" t="s">
@@ -6410,46 +6410,46 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>269</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="M5" s="26">
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O5" s="29">
         <v>4.9</v>
@@ -6464,17 +6464,17 @@
         <v>0</v>
       </c>
       <c r="S5" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="T5" s="25" t="s">
-        <v>258</v>
-      </c>
       <c r="U5" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="V5" s="14"/>
       <c r="W5" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X5" s="14"/>
       <c r="Y5" s="14" t="s">
@@ -6483,46 +6483,46 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="E6" s="24" t="s">
+      <c r="F6" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="G6" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="J6" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="K6" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="L6" s="24" t="s">
         <v>280</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>281</v>
       </c>
       <c r="M6" s="26">
         <v>1</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O6" s="27">
         <v>4.8</v>
@@ -6537,17 +6537,17 @@
         <v>0</v>
       </c>
       <c r="S6" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T6" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="T6" s="25" t="s">
-        <v>258</v>
-      </c>
       <c r="U6" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V6" s="24"/>
       <c r="W6" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X6" s="24"/>
       <c r="Y6" s="24" t="s">
@@ -6556,46 +6556,46 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="25" t="s">
         <v>285</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>286</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="I7" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>293</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>294</v>
       </c>
       <c r="M7" s="26">
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O7" s="29">
         <v>4.8</v>
@@ -6610,15 +6610,17 @@
         <v>0</v>
       </c>
       <c r="S7" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T7" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="T7" s="25" t="s">
-        <v>258</v>
-      </c>
       <c r="U7" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="V7" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="V7" s="14"/>
       <c r="W7" s="14" t="s">
         <v>297</v>
       </c>
@@ -6632,22 +6634,22 @@
         <v>299</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>300</v>
       </c>
       <c r="D8" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>301</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>302</v>
@@ -6683,17 +6685,17 @@
         <v>0</v>
       </c>
       <c r="S8" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T8" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T8" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U8" s="28" t="s">
         <v>308</v>
       </c>
       <c r="V8" s="24"/>
       <c r="W8" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X8" s="24"/>
       <c r="Y8" s="24" t="s">
@@ -6705,13 +6707,13 @@
         <v>310</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>286</v>
-      </c>
       <c r="D9" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>311</v>
@@ -6756,10 +6758,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T9" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T9" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U9" s="28" t="s">
         <v>320</v>
@@ -6778,22 +6780,22 @@
         <v>322</v>
       </c>
       <c r="B10" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>262</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>263</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>323</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>324</v>
@@ -6829,17 +6831,17 @@
         <v>0</v>
       </c>
       <c r="S10" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T10" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T10" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U10" s="28" t="s">
         <v>330</v>
       </c>
       <c r="V10" s="24"/>
       <c r="W10" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X10" s="24"/>
       <c r="Y10" s="24" t="s">
@@ -6851,16 +6853,16 @@
         <v>331</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>262</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>263</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>332</v>
@@ -6902,17 +6904,17 @@
         <v>0</v>
       </c>
       <c r="S11" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T11" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T11" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U11" s="28" t="s">
         <v>340</v>
       </c>
       <c r="V11" s="14"/>
       <c r="W11" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X11" s="14"/>
       <c r="Y11" s="14" t="s">
@@ -6924,13 +6926,13 @@
         <v>341</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>342</v>
@@ -6939,7 +6941,7 @@
         <v>343</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>344</v>
@@ -6975,17 +6977,17 @@
         <v>0</v>
       </c>
       <c r="S12" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T12" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T12" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U12" s="28" t="s">
         <v>350</v>
       </c>
       <c r="V12" s="24"/>
       <c r="W12" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X12" s="24"/>
       <c r="Y12" s="24" t="s">
@@ -6997,13 +6999,13 @@
         <v>351</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>286</v>
-      </c>
       <c r="D13" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>352</v>
@@ -7048,10 +7050,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="T13" s="25" t="s">
         <v>257</v>
-      </c>
-      <c r="T13" s="25" t="s">
-        <v>258</v>
       </c>
       <c r="U13" s="28" t="s">
         <v>359</v>
@@ -7070,16 +7072,16 @@
         <v>360</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>286</v>
-      </c>
       <c r="D14" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>361</v>
@@ -7244,7 +7246,7 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>374</v>
@@ -7259,13 +7261,13 @@
         <v>377</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H3" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>222</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>223</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>378</v>
@@ -7283,7 +7285,7 @@
         <v>382</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>383</v>
@@ -7319,10 +7321,10 @@
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I4" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>390</v>
@@ -7356,7 +7358,7 @@
         <v>396</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>397</v>
@@ -7374,10 +7376,10 @@
         <v>80</v>
       </c>
       <c r="H5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>247</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>248</v>
       </c>
       <c r="J5" s="14" t="s">
         <v>400</v>
@@ -7395,7 +7397,7 @@
         <v>401</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P5" s="14" t="s">
         <v>402</v>
@@ -7413,7 +7415,7 @@
         <v>405</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>406</v>
@@ -7431,10 +7433,10 @@
         <v>309</v>
       </c>
       <c r="H6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>400</v>
@@ -7470,7 +7472,7 @@
         <v>411</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>412</v>
@@ -7488,10 +7490,10 @@
         <v>115</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>400</v>
@@ -7509,7 +7511,7 @@
         <v>414</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P7" s="14" t="s">
         <v>415</v>
@@ -7527,7 +7529,7 @@
         <v>417</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>418</v>
@@ -7545,10 +7547,10 @@
         <v>125</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>400</v>
@@ -7566,7 +7568,7 @@
         <v>420</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P8" s="24" t="s">
         <v>421</v>
@@ -7584,7 +7586,7 @@
         <v>423</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>424</v>
@@ -7602,10 +7604,10 @@
         <v>140</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>400</v>
@@ -7641,7 +7643,7 @@
         <v>429</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>430</v>
@@ -7659,7 +7661,7 @@
         <v>99</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I10" s="24" t="s">
         <v>342</v>
@@ -7698,7 +7700,7 @@
         <v>435</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>436</v>
@@ -7716,10 +7718,10 @@
         <v>162</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>400</v>
@@ -7767,14 +7769,14 @@
         <v>298</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="24" t="s">
         <v>84</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J12" s="24" t="s">
         <v>390</v>
@@ -7792,7 +7794,7 @@
         <v>444</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P12" s="24" t="s">
         <v>445</v>
@@ -7826,7 +7828,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>352</v>
@@ -7941,7 +7943,7 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>375</v>
@@ -7953,10 +7955,10 @@
         <v>376</v>
       </c>
       <c r="F3" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>222</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>223</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>378</v>
@@ -7974,13 +7976,13 @@
         <v>382</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N3" s="21" t="s">
         <v>385</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>458</v>
@@ -8003,10 +8005,10 @@
         <v>371</v>
       </c>
       <c r="F4" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>390</v>
@@ -8037,7 +8039,7 @@
         <v>396</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>398</v>
@@ -8047,10 +8049,10 @@
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>247</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>248</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>400</v>
@@ -8068,7 +8070,7 @@
         <v>401</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14" t="s">
@@ -8083,7 +8085,7 @@
         <v>405</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>398</v>
@@ -8093,10 +8095,10 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>248</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>400</v>
@@ -8129,7 +8131,7 @@
         <v>411</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>398</v>
@@ -8139,10 +8141,10 @@
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>400</v>
@@ -8160,7 +8162,7 @@
         <v>414</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14" t="s">
@@ -8175,7 +8177,7 @@
         <v>417</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>398</v>
@@ -8185,10 +8187,10 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>400</v>
@@ -8206,7 +8208,7 @@
         <v>420</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N8" s="24"/>
       <c r="O8" s="24" t="s">
@@ -8221,7 +8223,7 @@
         <v>423</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>398</v>
@@ -8231,10 +8233,10 @@
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>400</v>
@@ -8267,7 +8269,7 @@
         <v>429</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>398</v>
@@ -8277,7 +8279,7 @@
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>342</v>
@@ -8313,7 +8315,7 @@
         <v>435</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>398</v>
@@ -8323,10 +8325,10 @@
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>400</v>
@@ -8365,7 +8367,7 @@
         <v>443</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>298</v>
@@ -8374,7 +8376,7 @@
         <v>84</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>390</v>
@@ -8392,7 +8394,7 @@
         <v>444</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
@@ -8417,7 +8419,7 @@
         <v>321</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>352</v>
@@ -8485,7 +8487,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8533,10 +8535,10 @@
         <v>463</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>222</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>223</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>464</v>
@@ -8563,19 +8565,19 @@
         <v>375</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N3" s="21" t="s">
         <v>380</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>471</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8586,10 +8588,10 @@
         <v>361</v>
       </c>
       <c r="C4" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>247</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>248</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>365</v>
@@ -8631,25 +8633,25 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>84</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="G5" s="32" t="s">
         <v>289</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>290</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>474</v>
@@ -8673,13 +8675,13 @@
         <v>461</v>
       </c>
       <c r="O5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="P5" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="P5" s="14" t="s">
-        <v>258</v>
-      </c>
       <c r="Q5" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8690,7 +8692,7 @@
         <v>312</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>311</v>
@@ -8726,10 +8728,10 @@
         <v>461</v>
       </c>
       <c r="O6" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="P6" s="24" t="s">
         <v>257</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>258</v>
       </c>
       <c r="Q6" s="24" t="s">
         <v>320</v>
@@ -8743,7 +8745,7 @@
         <v>353</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>352</v>
@@ -8779,10 +8781,10 @@
         <v>461</v>
       </c>
       <c r="O7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="P7" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="Q7" s="14" t="s">
         <v>359</v>
@@ -8961,13 +8963,13 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>487</v>
@@ -9060,46 +9062,46 @@
         <v>509</v>
       </c>
       <c r="AI3" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>232</v>
       </c>
       <c r="AK3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="AL3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AM3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="AM3" s="21" t="s">
+      <c r="AN3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="AN3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="AO3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="AP3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="AQ3" s="21" t="s">
+      <c r="AR3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="AR3" s="21" t="s">
+      <c r="AS3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="AS3" s="21" t="s">
+      <c r="AT3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AT3" s="21" t="s">
+      <c r="AU3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AU3" s="21" t="s">
+      <c r="AV3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="AV3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AW3" s="21" t="s">
         <v>512</v>
@@ -9241,13 +9243,13 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>515</v>
@@ -9304,46 +9306,46 @@
         <v>509</v>
       </c>
       <c r="W3" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>232</v>
       </c>
       <c r="Y3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="Z3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AB3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="AC3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="AD3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AE3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AF3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="AF3" s="21" t="s">
+      <c r="AG3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="AG3" s="21" t="s">
+      <c r="AH3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AH3" s="21" t="s">
+      <c r="AI3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AK3" s="21" t="s">
         <v>512</v>
@@ -9503,16 +9505,16 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>526</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>487</v>
@@ -9590,46 +9592,46 @@
         <v>509</v>
       </c>
       <c r="AE3" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AF3" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>232</v>
       </c>
       <c r="AG3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="AH3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AI3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="AK3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="AL3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AM3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="AM3" s="21" t="s">
+      <c r="AN3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="AN3" s="21" t="s">
+      <c r="AO3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="AO3" s="21" t="s">
+      <c r="AP3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AP3" s="21" t="s">
+      <c r="AQ3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AQ3" s="21" t="s">
+      <c r="AR3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="AR3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AS3" s="21" t="s">
         <v>512</v>
@@ -9782,13 +9784,13 @@
         <v>175</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>487</v>
@@ -9857,46 +9859,46 @@
         <v>509</v>
       </c>
       <c r="AA3" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB3" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>232</v>
       </c>
       <c r="AC3" s="21" t="s">
         <v>510</v>
       </c>
       <c r="AD3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="AE3" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AF3" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="AG3" s="21" t="s">
         <v>511</v>
       </c>
       <c r="AH3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="AJ3" s="21" t="s">
+      <c r="AK3" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="AK3" s="21" t="s">
+      <c r="AL3" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AL3" s="21" t="s">
+      <c r="AM3" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AM3" s="21" t="s">
+      <c r="AN3" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="AN3" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AO3" s="21" t="s">
         <v>512</v>

--- a/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
+++ b/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="684">
   <si>
     <t>韩国济州岛旅行 · 最终方案首页</t>
   </si>
@@ -36,7 +36,7 @@
     <t>网站只读取这一页作为最终攻略；后面的工作表都是候选资料和处理记录。</t>
   </si>
   <si>
-    <t>黄色单元格可直接修改；保存 Excel 后约 4 秒同步网站。当前已确定 15/18 项，待补充 3 项。</t>
+    <t>黄色单元格可直接修改；保存 Excel 后约 4 秒同步网站。当前已确定 15/19 项，待补充 4 项。</t>
   </si>
   <si>
     <t>一、基础信息  ·  网站顶部与旅行概览</t>
@@ -96,16 +96,28 @@
     <t>人均预算</t>
   </si>
   <si>
-    <t>¥1,000–1,500 / 人（不含往返济州机票）</t>
+    <t>¥6,000 / 人（包含往返济州机票）</t>
   </si>
   <si>
     <t>可填写数字或预算区间</t>
   </si>
   <si>
+    <t>往返机票 / 人</t>
+  </si>
+  <si>
+    <t>待填写实际含税票价（含托运行李）</t>
+  </si>
+  <si>
+    <t>待补充</t>
+  </si>
+  <si>
+    <t>填写含税、行李额后的每人实际往返票价</t>
+  </si>
+  <si>
     <t>方案说明</t>
   </si>
   <si>
-    <t>六人按真实消费重算：正餐约 ¥100/人，穿插民宿做饭与一起吃宵夜；岛内公交优先、必要时短途拼车，不默认全程打车或包车；贵景点可换成免费海岸、市场和步道。</t>
+    <t>六人总预算约 ¥36,000（¥6,000/人，包含往返济州机票）；机票实际价格确认后，再由 AI 分配住宿、餐饮、岛内交通、游玩和机动金。餐饮仍按正餐约 ¥100/人并可穿插民宿做饭，岛内交通公交优先、必要时短途拼车。</t>
   </si>
   <si>
     <t>网站首页的行程摘要</t>
@@ -118,9 +130,6 @@
   </si>
   <si>
     <t>待选择｜济州市区六人酒店或公寓</t>
-  </si>
-  <si>
-    <t>待补充</t>
   </si>
   <si>
     <t>确定住宿后填写真实名称</t>
@@ -2955,7 +2964,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" ht="46" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
@@ -2963,11 +2972,11 @@
         <v>25</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="7" t="s">
-        <v>6</v>
+      <c r="D13" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -2977,9 +2986,31 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
+    <row r="14" ht="70" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
     <row r="15" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2995,17 +3026,17 @@
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -3017,17 +3048,17 @@
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -3039,17 +3070,17 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -3061,17 +3092,17 @@
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -3083,17 +3114,17 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -3105,17 +3136,17 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -3127,17 +3158,17 @@
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -3149,17 +3180,17 @@
     </row>
     <row r="23" ht="46" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -3171,17 +3202,17 @@
     </row>
     <row r="24" ht="46" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -3193,15 +3224,15 @@
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -3213,7 +3244,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -3229,525 +3260,525 @@
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I29" s="12">
         <v>15</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K30" s="16"/>
       <c r="L30" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I31" s="12">
         <v>30</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I32" s="15">
         <v>100</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I33" s="12">
         <v>35</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I34" s="15">
         <v>25</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I35" s="12">
         <v>100</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K35" s="13"/>
       <c r="L35" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I36" s="15">
         <v>10</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="H37" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I37" s="12">
         <v>70</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I38" s="15">
         <v>25</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K38" s="16"/>
       <c r="L38" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I39" s="12">
         <v>20</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I40" s="15">
         <v>60</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K40" s="16"/>
       <c r="L40" s="14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I41" s="12">
         <v>15</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3763,188 +3794,188 @@
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>186</v>
-      </c>
       <c r="G46" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" ht="38" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="45">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -3965,6 +3996,8 @@
     <mergeCell ref="E12:L12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="E13:L13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E14:L14"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="E16:L16"/>
@@ -4040,7 +4073,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4078,7 +4111,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4116,160 +4149,160 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="N3" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>502</v>
-      </c>
       <c r="P3" s="21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="T3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D4" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>264</v>
-      </c>
       <c r="F4" s="32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G4" s="35"/>
       <c r="H4" s="32" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="S4" s="27">
         <v>4.9</v>
@@ -4278,10 +4311,10 @@
         <v>1</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="W4" s="24">
         <v>0</v>
@@ -4294,78 +4327,78 @@
       </c>
       <c r="Z4" s="24"/>
       <c r="AA4" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AC4" s="24" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AD4" s="24"/>
       <c r="AE4" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AF4" s="24"/>
       <c r="AG4" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AH4" s="24" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G5" s="35"/>
       <c r="H5" s="32" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="S5" s="29">
         <v>4.5</v>
@@ -4374,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="W5" s="14">
         <v>0</v>
@@ -4390,78 +4423,78 @@
       </c>
       <c r="Z5" s="14"/>
       <c r="AA5" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AB5" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AC5" s="14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AF5" s="14"/>
       <c r="AG5" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="32" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M6" s="32" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="S6" s="27">
         <v>4.4</v>
@@ -4470,10 +4503,10 @@
         <v>1</v>
       </c>
       <c r="U6" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="V6" s="24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="W6" s="24">
         <v>0</v>
@@ -4486,78 +4519,78 @@
       </c>
       <c r="Z6" s="24"/>
       <c r="AA6" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AB6" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AC6" s="24" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AD6" s="24"/>
       <c r="AE6" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AF6" s="24"/>
       <c r="AG6" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AH6" s="24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D7" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>333</v>
-      </c>
       <c r="F7" s="32" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G7" s="35"/>
       <c r="H7" s="32" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M7" s="32" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="S7" s="29">
         <v>4.5</v>
@@ -4566,10 +4599,10 @@
         <v>1</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="W7" s="14">
         <v>0</v>
@@ -4582,24 +4615,24 @@
       </c>
       <c r="Z7" s="14"/>
       <c r="AA7" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AD7" s="14"/>
       <c r="AE7" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AF7" s="14"/>
       <c r="AG7" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -4643,7 +4676,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4670,7 +4703,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4697,108 +4730,108 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D4" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>249</v>
-      </c>
       <c r="F4" s="32" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J4" s="26">
         <v>1</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="L4" s="24">
         <v>0</v>
@@ -4811,59 +4844,59 @@
       </c>
       <c r="O4" s="24"/>
       <c r="P4" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="S4" s="24"/>
       <c r="T4" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="U4" s="24"/>
       <c r="V4" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="W4" s="24" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J5" s="26">
         <v>1</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -4876,59 +4909,59 @@
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="U5" s="14"/>
       <c r="V5" s="14" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D6" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="E6" s="32" t="s">
-        <v>275</v>
-      </c>
       <c r="F6" s="32" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J6" s="26">
         <v>1</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="L6" s="24">
         <v>0</v>
@@ -4941,24 +4974,24 @@
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="S6" s="24"/>
       <c r="T6" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="U6" s="24"/>
       <c r="V6" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="W6" s="24" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4995,7 +5028,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -5012,7 +5045,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -5029,552 +5062,552 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I4" s="24">
         <v>15</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M5" s="14"/>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I6" s="24">
         <v>30</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I7" s="14">
         <v>100</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I8" s="24">
         <v>35</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I9" s="14">
         <v>25</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I10" s="24">
         <v>100</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L10" s="24"/>
       <c r="M10" s="24"/>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I11" s="14">
         <v>10</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>105</v>
-      </c>
       <c r="H12" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I12" s="24">
         <v>70</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I13" s="14">
         <v>25</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I14" s="24">
         <v>20</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I15" s="14">
         <v>60</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I16" s="24">
         <v>15</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5607,7 +5640,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -5619,7 +5652,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -5631,184 +5664,184 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5839,27 +5872,27 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5870,18 +5903,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5892,7 +5925,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5903,95 +5936,95 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -6022,137 +6055,137 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B5" s="14">
         <v>10</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B6" s="24">
         <v>10</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="B8" s="24">
         <v>11</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B10" s="24">
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B11" s="14">
         <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B12" s="24">
         <v>6</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -6202,7 +6235,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6231,7 +6264,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6260,123 +6293,123 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M4" s="26">
         <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O4" s="27">
         <v>5</v>
@@ -6391,65 +6424,65 @@
         <v>0</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T4" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U4" s="28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V4" s="24"/>
       <c r="W4" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X4" s="24"/>
       <c r="Y4" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M5" s="26">
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O5" s="29">
         <v>4.9</v>
@@ -6464,65 +6497,65 @@
         <v>0</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U5" s="28" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="V5" s="14"/>
       <c r="W5" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X5" s="14"/>
       <c r="Y5" s="14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M6" s="26">
         <v>1</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O6" s="27">
         <v>4.8</v>
@@ -6537,65 +6570,65 @@
         <v>0</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U6" s="28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="V6" s="24"/>
       <c r="W6" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X6" s="24"/>
       <c r="Y6" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M7" s="26">
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O7" s="29">
         <v>4.8</v>
@@ -6610,67 +6643,67 @@
         <v>0</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U7" s="28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Y7" s="14"/>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M8" s="26">
         <v>1</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="O8" s="27">
         <v>4.7</v>
@@ -6685,65 +6718,65 @@
         <v>0</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T8" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U8" s="28" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="V8" s="24"/>
       <c r="W8" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X8" s="24"/>
       <c r="Y8" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M9" s="26">
         <v>1</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O9" s="29">
         <v>4.6</v>
@@ -6758,65 +6791,65 @@
         <v>0</v>
       </c>
       <c r="S9" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T9" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U9" s="28" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="V9" s="14"/>
       <c r="W9" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Y9" s="14"/>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M10" s="26">
         <v>1</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="O10" s="27">
         <v>4.5</v>
@@ -6831,65 +6864,65 @@
         <v>0</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U10" s="28" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="V10" s="24"/>
       <c r="W10" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X10" s="24"/>
       <c r="Y10" s="24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M11" s="26">
         <v>1</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O11" s="29">
         <v>4.5</v>
@@ -6904,65 +6937,65 @@
         <v>0</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U11" s="28" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="V11" s="14"/>
       <c r="W11" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X11" s="14"/>
       <c r="Y11" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M12" s="26">
         <v>1</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O12" s="27">
         <v>4.4</v>
@@ -6977,65 +7010,65 @@
         <v>0</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T12" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U12" s="28" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="V12" s="24"/>
       <c r="W12" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X12" s="24"/>
       <c r="Y12" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M13" s="26">
         <v>1</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O13" s="29">
         <v>4.4</v>
@@ -7050,65 +7083,65 @@
         <v>0</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U13" s="28" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="V13" s="14"/>
       <c r="W13" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="X13" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Y13" s="14"/>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M14" s="26">
         <v>1</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O14" s="27">
         <v>3.5</v>
@@ -7123,18 +7156,18 @@
         <v>0</v>
       </c>
       <c r="S14" s="25" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="T14" s="25" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="U14" s="28"/>
       <c r="V14" s="24"/>
       <c r="W14" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="X14" s="24" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Y14" s="24"/>
     </row>
@@ -7197,7 +7230,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -7220,7 +7253,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -7243,623 +7276,623 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M4" s="24">
         <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M5" s="14">
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="14" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M6" s="24">
         <v>1</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="24" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M7" s="14">
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M8" s="24">
         <v>1</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R8" s="24"/>
       <c r="S8" s="24" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M9" s="14">
         <v>1</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M10" s="24">
         <v>1</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="24" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M11" s="14">
         <v>1</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M12" s="24">
         <v>1</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="R12" s="24"/>
       <c r="S12" s="24" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M13" s="14">
         <v>2</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="R13" s="14"/>
       <c r="S13" s="14" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -7900,7 +7933,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -7920,7 +7953,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -7940,512 +7973,512 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J4" s="24">
         <v>1</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J5" s="14">
         <v>1</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J6" s="24">
         <v>1</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N6" s="24"/>
       <c r="O6" s="24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J7" s="14">
         <v>1</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J8" s="24">
         <v>1</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N8" s="24"/>
       <c r="O8" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J9" s="14">
         <v>1</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J10" s="24">
         <v>1</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N10" s="24"/>
       <c r="O10" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J11" s="14">
         <v>1</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J12" s="24">
         <v>1</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J13" s="14">
         <v>2</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
       <c r="P13" s="14" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -8487,7 +8520,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8508,7 +8541,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -8529,265 +8562,265 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M3" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q3" s="21" t="s">
         <v>241</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>380</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E4" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="F4" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="F4" s="32" t="s">
-        <v>362</v>
-      </c>
       <c r="G4" s="32" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E5" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="F5" s="32" t="s">
-        <v>288</v>
-      </c>
       <c r="G5" s="32" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M5" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q5" s="14" t="s">
         <v>298</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E6" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>313</v>
-      </c>
       <c r="G6" s="32" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -8854,7 +8887,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8907,7 +8940,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -8960,151 +8993,151 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AH3" s="23" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AI3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AT3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AU3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AV3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -9158,7 +9191,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9199,7 +9232,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9240,115 +9273,115 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>523</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="V3" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="W3" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="AK3" s="21" t="s">
         <v>515</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>487</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>516</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>517</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>518</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>519</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>520</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>521</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>522</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>502</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>498</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>507</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>508</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>509</v>
-      </c>
-      <c r="W3" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>510</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>511</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="AG3" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="AH3" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="AI3" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="AK3" s="21" t="s">
-        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -9404,7 +9437,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9453,7 +9486,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9502,139 +9535,139 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>487</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>527</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>517</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>528</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>531</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>532</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>533</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>539</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>540</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>522</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>523</v>
-      </c>
       <c r="Y3" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="Z3" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="Z3" s="21" t="s">
-        <v>502</v>
-      </c>
       <c r="AA3" s="21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AE3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -9691,7 +9724,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9736,7 +9769,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9781,127 +9814,127 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="Z3" s="23" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AA3" s="22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
+++ b/outputs/019fa660-42f1-74a1-ab98-31c99abb6300/韩国济州岛旅行共创.xlsx
@@ -8,17 +8,18 @@
     <sheet sheetId="2" name="候选决策台" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="投递汇总" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="处理报告" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="团队需求" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="住宿候选" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="美食餐饮" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="密室候选" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="室内休闲" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="景点户外" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="攻略文章" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="三日行程" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="预订清单" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="项目设置" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="项目总览" state="visible" r:id="rId18"/>
+    <sheet sheetId="5" name="AI审阅建议" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="团队需求" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="住宿候选" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="美食餐饮" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="密室候选" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="室内休闲" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="景点户外" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="攻略文章" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="三日行程" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="预订清单" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="项目设置" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="项目总览" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'行程首页'!$A1:$L50</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="755">
   <si>
     <t>韩国济州岛旅行 · 最终方案首页</t>
   </si>
@@ -738,6 +739,18 @@
     <t>AI推荐分</t>
   </si>
   <si>
+    <t>AI评分说明</t>
+  </si>
+  <si>
+    <t>AI建议时段</t>
+  </si>
+  <si>
+    <t>AI候选线索</t>
+  </si>
+  <si>
+    <t>AI估价依据</t>
+  </si>
+  <si>
     <t>想去票</t>
   </si>
   <si>
@@ -807,6 +820,9 @@
     <t>K-ETA 是否适用需订票前确认；个人入境资格由边检最终判断</t>
   </si>
   <si>
+    <t>等待说明</t>
+  </si>
+  <si>
     <t>拟定</t>
   </si>
   <si>
@@ -1425,6 +1441,210 @@
     <t>已生成候选资料并写入 Excel</t>
   </si>
   <si>
+    <t>AI审阅建议</t>
+  </si>
+  <si>
+    <t>DeepSeek 对当前 Excel 与行程快照的审阅记录；建议不会直接覆盖投票、入选结论或人工锁定字段。</t>
+  </si>
+  <si>
+    <t>审阅ID</t>
+  </si>
+  <si>
+    <t>建议ID</t>
+  </si>
+  <si>
+    <t>生成时间</t>
+  </si>
+  <si>
+    <t>审阅摘要</t>
+  </si>
+  <si>
+    <t>建议类型</t>
+  </si>
+  <si>
+    <t>修改对象</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>当前内容</t>
+  </si>
+  <si>
+    <t>AI建议</t>
+  </si>
+  <si>
+    <t>修改理由</t>
+  </si>
+  <si>
+    <t>置信度</t>
+  </si>
+  <si>
+    <t>依据类型</t>
+  </si>
+  <si>
+    <t>应用结果</t>
+  </si>
+  <si>
+    <t>review-00111395-14eb-4f70-bb13-ac7507bd26f3</t>
+  </si>
+  <si>
+    <t>suggestion-1-f4f788da</t>
+  </si>
+  <si>
+    <t>2026-07-29T07:07:56.703Z</t>
+  </si>
+  <si>
+    <t>济州岛3天2晚六人度假方案：轻松为主，东线自然+市区美食｜方案以轻松度假为核心，东线自然景观（城山日出峰、涉地可支）搭配市区市场与美食，公交优先，预算可控。但住宿、机票、部分餐饮未定，第3天涯月行程与返程时间存在冲突。</t>
+  </si>
+  <si>
+    <t>价格预测</t>
+  </si>
+  <si>
+    <t>预算总览</t>
+  </si>
+  <si>
+    <t>known.min</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>已知费用（不含机票）约805元/人，但机票未定，总预算6000元/人，机票需控制在约5000元/人以内。</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>预算计算</t>
+  </si>
+  <si>
+    <t>待处理</t>
+  </si>
+  <si>
+    <t>suggestion-2-c84d814e</t>
+  </si>
+  <si>
+    <t>AI估价：六人两晚约¥2,400–3,000</t>
+  </si>
+  <si>
+    <t>根据济州市区6人公寓或酒店8月旺季价格，两晚总价约2400-3000元。</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>市场调研</t>
+  </si>
+  <si>
+    <t>suggestion-3-643ec59e</t>
+  </si>
+  <si>
+    <t>推荐分</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>经典景点，适合团队，但需注意体力与天气。</t>
+  </si>
+  <si>
+    <t>景点评价</t>
+  </si>
+  <si>
+    <t>suggestion-4-f7e7a9f8</t>
+  </si>
+  <si>
+    <t>优缺点</t>
+  </si>
+  <si>
+    <t>整体方案</t>
+  </si>
+  <si>
+    <t>pros</t>
+  </si>
+  <si>
+    <t>轻松节奏，东线自然与市区美食结合，公交优先节省费用。</t>
+  </si>
+  <si>
+    <t>方案符合团队度假需求，行程不紧凑。</t>
+  </si>
+  <si>
+    <t>行程分析</t>
+  </si>
+  <si>
+    <t>suggestion-5-db6885fc</t>
+  </si>
+  <si>
+    <t>cons</t>
+  </si>
+  <si>
+    <t>第3天涯月行程与返程时间冲突，若航班较早则无法完成；住宿、机票、部分餐饮未定。</t>
+  </si>
+  <si>
+    <t>涯月距机场约40分钟车程，若航班在15:00前则时间紧张。</t>
+  </si>
+  <si>
+    <t>时间计算</t>
+  </si>
+  <si>
+    <t>suggestion-6-fe1496d9</t>
+  </si>
+  <si>
+    <t>missingFields</t>
+  </si>
+  <si>
+    <t>机票价格、住宿具体信息、部分餐厅、公交班次、行李寄存。</t>
+  </si>
+  <si>
+    <t>关键信息缺失，影响预算和行程可行性。</t>
+  </si>
+  <si>
+    <t>数据检查</t>
+  </si>
+  <si>
+    <t>suggestion-7-d2e9be38</t>
+  </si>
+  <si>
+    <t>建议时段</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>10:00-13:00</t>
+  </si>
+  <si>
+    <t>建议调整为08:30-11:00，或根据航班时间取消</t>
+  </si>
+  <si>
+    <t>若返程航班在15:00后，可保留但需提前；若航班较早则取消。</t>
+  </si>
+  <si>
+    <t>时间冲突分析</t>
+  </si>
+  <si>
+    <t>suggestion-8-b0bcc0e8</t>
+  </si>
+  <si>
+    <t>路线冲突</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>第3天行程与返程时间冲突，建议缩短或移至第1天下午（若航班早到）</t>
+  </si>
+  <si>
+    <t>第3天上午去涯月，下午返程，若航班在15:00前则无法完成。</t>
+  </si>
+  <si>
+    <t>时间线分析</t>
+  </si>
+  <si>
     <t>团队成员写下的愿望和约束，只作为匹配条件；标记“采用”表示确认这条需求，不代表已经选定真实商户。</t>
   </si>
   <si>
@@ -1566,9 +1786,6 @@
     <t>缺点</t>
   </si>
   <si>
-    <t>推荐分</t>
-  </si>
-  <si>
     <t>证据摘要</t>
   </si>
   <si>
@@ -1921,9 +2138,6 @@
   </si>
   <si>
     <t>设置项</t>
-  </si>
-  <si>
-    <t>当前内容</t>
   </si>
   <si>
     <t>说明</t>
@@ -4043,7 +4257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4052,28 +4266,33 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" style="33" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="16" width="16" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="16" style="18" customWidth="1"/>
-    <col min="20" max="20" width="18" style="17" customWidth="1"/>
-    <col min="21" max="22" width="30" customWidth="1"/>
-    <col min="23" max="28" width="18" customWidth="1"/>
-    <col min="29" max="29" width="30" customWidth="1"/>
-    <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="31" max="31" width="16" customWidth="1"/>
-    <col min="32" max="32" width="38" customWidth="1"/>
-    <col min="33" max="33" width="36" customWidth="1"/>
-    <col min="34" max="34" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" style="33" customWidth="1"/>
+    <col min="8" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
+    <col min="14" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="30" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="25" width="30" customWidth="1"/>
+    <col min="26" max="26" width="16" style="18" customWidth="1"/>
+    <col min="27" max="27" width="18" style="17" customWidth="1"/>
+    <col min="28" max="29" width="30" customWidth="1"/>
+    <col min="30" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="38" width="16" customWidth="1"/>
+    <col min="39" max="39" width="38" customWidth="1"/>
+    <col min="40" max="40" width="36" customWidth="1"/>
+    <col min="41" max="41" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>555</v>
+        <v>616</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4108,10 +4327,17 @@
       <c r="AF1" s="19"/>
       <c r="AG1" s="19"/>
       <c r="AH1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4146,6 +4372,261 @@
       <c r="AF2" s="20"/>
       <c r="AG2" s="20"/>
       <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>618</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="Z3" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="AK3" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="AL3" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="AM3" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:AO4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A2:AO2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L韩国济州岛出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" style="33" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="16" style="18" customWidth="1"/>
+    <col min="20" max="20" width="18" style="17" customWidth="1"/>
+    <col min="21" max="22" width="30" customWidth="1"/>
+    <col min="23" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="32" max="32" width="38" customWidth="1"/>
+    <col min="33" max="33" width="36" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -4161,49 +4642,49 @@
         <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>557</v>
+        <v>629</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>558</v>
+        <v>630</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>525</v>
+        <v>597</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>559</v>
+        <v>631</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>560</v>
+        <v>632</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>561</v>
+        <v>633</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>526</v>
+        <v>598</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>505</v>
+        <v>578</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>71</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>562</v>
+        <v>634</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>563</v>
+        <v>635</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="T3" s="22" t="s">
         <v>233</v>
@@ -4212,97 +4693,97 @@
         <v>234</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>515</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="35"/>
       <c r="H4" s="32" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>564</v>
+        <v>636</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>567</v>
+        <v>639</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>568</v>
+        <v>640</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="P4" s="24" t="s">
         <v>127</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>570</v>
+        <v>642</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>571</v>
+        <v>643</v>
       </c>
       <c r="S4" s="27">
         <v>4.9</v>
@@ -4311,10 +4792,10 @@
         <v>1</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="W4" s="24">
         <v>0</v>
@@ -4327,78 +4808,78 @@
       </c>
       <c r="Z4" s="24"/>
       <c r="AA4" s="24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AC4" s="24" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AD4" s="24"/>
       <c r="AE4" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AF4" s="24"/>
       <c r="AG4" s="24" t="s">
         <v>128</v>
       </c>
       <c r="AH4" s="24" t="s">
-        <v>573</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>141</v>
       </c>
       <c r="G5" s="35"/>
       <c r="H5" s="32" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>574</v>
+        <v>646</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>575</v>
+        <v>647</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>577</v>
+        <v>649</v>
       </c>
       <c r="P5" s="14" t="s">
         <v>127</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>578</v>
+        <v>650</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>579</v>
+        <v>651</v>
       </c>
       <c r="S5" s="29">
         <v>4.5</v>
@@ -4407,10 +4888,10 @@
         <v>1</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="W5" s="14">
         <v>0</v>
@@ -4423,78 +4904,78 @@
       </c>
       <c r="Z5" s="14"/>
       <c r="AA5" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AB5" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AC5" s="14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AF5" s="14"/>
       <c r="AG5" s="14" t="s">
         <v>143</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>581</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>582</v>
+        <v>654</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="32" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>583</v>
+        <v>655</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>584</v>
+        <v>656</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>585</v>
+        <v>657</v>
       </c>
       <c r="M6" s="32" t="s">
         <v>101</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>586</v>
+        <v>658</v>
       </c>
       <c r="P6" s="24" t="s">
         <v>101</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>587</v>
+        <v>659</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>588</v>
+        <v>660</v>
       </c>
       <c r="S6" s="27">
         <v>4.4</v>
@@ -4503,10 +4984,10 @@
         <v>1</v>
       </c>
       <c r="U6" s="24" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="V6" s="24" t="s">
-        <v>589</v>
+        <v>661</v>
       </c>
       <c r="W6" s="24">
         <v>0</v>
@@ -4519,78 +5000,78 @@
       </c>
       <c r="Z6" s="24"/>
       <c r="AA6" s="24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AB6" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AC6" s="24" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AD6" s="24"/>
       <c r="AE6" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AF6" s="24"/>
       <c r="AG6" s="24" t="s">
         <v>102</v>
       </c>
       <c r="AH6" s="24" t="s">
-        <v>590</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>591</v>
+        <v>663</v>
       </c>
       <c r="G7" s="35"/>
       <c r="H7" s="32" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>592</v>
+        <v>664</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>593</v>
+        <v>665</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>594</v>
+        <v>666</v>
       </c>
       <c r="M7" s="32" t="s">
-        <v>595</v>
+        <v>667</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>577</v>
+        <v>649</v>
       </c>
       <c r="P7" s="14" t="s">
         <v>101</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>596</v>
+        <v>668</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>597</v>
+        <v>669</v>
       </c>
       <c r="S7" s="29">
         <v>4.5</v>
@@ -4599,10 +5080,10 @@
         <v>1</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>598</v>
+        <v>670</v>
       </c>
       <c r="W7" s="14">
         <v>0</v>
@@ -4615,24 +5096,24 @@
       </c>
       <c r="Z7" s="14"/>
       <c r="AA7" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AD7" s="14"/>
       <c r="AE7" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AF7" s="14"/>
       <c r="AG7" s="14" t="s">
         <v>165</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>599</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -4649,7 +5130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4676,7 +5157,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4703,7 +5184,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>600</v>
+        <v>672</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4733,7 +5214,7 @@
         <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>601</v>
+        <v>673</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>225</v>
@@ -4742,16 +5223,16 @@
         <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>602</v>
+        <v>674</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>603</v>
+        <v>675</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>234</v>
@@ -4760,78 +5241,78 @@
         <v>233</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>515</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>605</v>
+        <v>677</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>606</v>
+        <v>678</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>607</v>
+        <v>679</v>
       </c>
       <c r="J4" s="26">
         <v>1</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>608</v>
+        <v>680</v>
       </c>
       <c r="L4" s="24">
         <v>0</v>
@@ -4844,59 +5325,59 @@
       </c>
       <c r="O4" s="24"/>
       <c r="P4" s="24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="S4" s="24"/>
       <c r="T4" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="U4" s="24"/>
       <c r="V4" s="24" t="s">
         <v>83</v>
       </c>
       <c r="W4" s="24" t="s">
-        <v>609</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>610</v>
+        <v>682</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>611</v>
+        <v>683</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>612</v>
+        <v>684</v>
       </c>
       <c r="J5" s="26">
         <v>1</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>613</v>
+        <v>685</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -4909,59 +5390,59 @@
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="U5" s="14"/>
       <c r="V5" s="14" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>614</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>615</v>
+        <v>687</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>616</v>
+        <v>688</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>617</v>
+        <v>689</v>
       </c>
       <c r="J6" s="26">
         <v>1</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>618</v>
+        <v>690</v>
       </c>
       <c r="L6" s="24">
         <v>0</v>
@@ -4974,24 +5455,24 @@
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="S6" s="24"/>
       <c r="T6" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="U6" s="24"/>
       <c r="V6" s="24" t="s">
         <v>118</v>
       </c>
       <c r="W6" s="24" t="s">
-        <v>619</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -5008,7 +5489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5028,7 +5509,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>620</v>
+        <v>692</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -5045,7 +5526,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>621</v>
+        <v>693</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -5074,10 +5555,10 @@
         <v>65</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>622</v>
+        <v>694</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>623</v>
+        <v>695</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>35</v>
@@ -5086,16 +5567,16 @@
         <v>69</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>624</v>
+        <v>696</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>71</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>563</v>
+        <v>635</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>625</v>
+        <v>697</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>72</v>
@@ -5136,7 +5617,7 @@
         <v>84</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>83</v>
@@ -5175,7 +5656,7 @@
         <v>93</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M5" s="14"/>
     </row>
@@ -5214,7 +5695,7 @@
         <v>103</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M6" s="24" t="s">
         <v>102</v>
@@ -5292,7 +5773,7 @@
         <v>119</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M8" s="24" t="s">
         <v>118</v>
@@ -5333,7 +5814,7 @@
         <v>129</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>128</v>
@@ -5411,7 +5892,7 @@
         <v>144</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M11" s="14" t="s">
         <v>143</v>
@@ -5526,7 +6007,7 @@
         <v>166</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>165</v>
@@ -5604,7 +6085,7 @@
         <v>176</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>83</v>
@@ -5624,7 +6105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5640,7 +6121,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -5652,7 +6133,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>627</v>
+        <v>699</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -5858,7 +6339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5872,27 +6353,27 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>628</v>
+        <v>700</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>629</v>
+        <v>701</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>630</v>
+        <v>702</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>631</v>
+        <v>479</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5903,18 +6384,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>633</v>
+        <v>704</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>634</v>
+        <v>705</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>635</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5925,7 +6406,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5936,40 +6417,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>637</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>638</v>
+        <v>709</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>639</v>
+        <v>710</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>640</v>
+        <v>711</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>641</v>
+        <v>712</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>642</v>
+        <v>713</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>643</v>
+        <v>714</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>644</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5977,54 +6458,54 @@
         <v>153</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>645</v>
+        <v>716</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>646</v>
+        <v>717</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>647</v>
+        <v>718</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>648</v>
+        <v>719</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>649</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>650</v>
+        <v>721</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>651</v>
+        <v>722</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>652</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>653</v>
+        <v>724</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>654</v>
+        <v>725</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>655</v>
+        <v>726</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>656</v>
+        <v>727</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>657</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -6041,7 +6522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6055,137 +6536,137 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>658</v>
+        <v>729</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>659</v>
+        <v>730</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>660</v>
+        <v>731</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>661</v>
+        <v>732</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>662</v>
+        <v>733</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>663</v>
+        <v>734</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>664</v>
+        <v>735</v>
       </c>
       <c r="B5" s="14">
         <v>10</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>665</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>666</v>
+        <v>737</v>
       </c>
       <c r="B6" s="24">
         <v>10</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>667</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>668</v>
+        <v>739</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>669</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>670</v>
+        <v>741</v>
       </c>
       <c r="B8" s="24">
         <v>11</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>671</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>672</v>
+        <v>743</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>673</v>
+        <v>744</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>674</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>675</v>
+        <v>746</v>
       </c>
       <c r="B10" s="24">
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>676</v>
+        <v>747</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>677</v>
+        <v>748</v>
       </c>
       <c r="B11" s="14">
         <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>678</v>
+        <v>749</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>679</v>
+        <v>750</v>
       </c>
       <c r="B12" s="24">
         <v>6</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>680</v>
+        <v>751</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>681</v>
+        <v>752</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>682</v>
+        <v>753</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>683</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -6208,7 +6689,7 @@
     <tabColor rgb="D9703E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6223,17 +6704,21 @@
     <col min="13" max="13" width="13" style="17" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
     <col min="15" max="15" width="12" style="18" customWidth="1"/>
-    <col min="16" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="28" customWidth="1"/>
-    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="38" customWidth="1"/>
-    <col min="25" max="25" width="36" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="25" max="25" width="28" customWidth="1"/>
+    <col min="26" max="26" width="22" customWidth="1"/>
+    <col min="27" max="27" width="12" customWidth="1"/>
+    <col min="28" max="28" width="38" customWidth="1"/>
+    <col min="29" max="29" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>220</v>
       </c>
@@ -6261,8 +6746,12 @@
       <c r="W1" s="19"/>
       <c r="X1" s="19"/>
       <c r="Y1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>221</v>
       </c>
@@ -6290,8 +6779,12 @@
       <c r="W2" s="20"/>
       <c r="X2" s="20"/>
       <c r="Y2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>178</v>
       </c>
@@ -6367,815 +6860,893 @@
       <c r="Y3" s="21" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z3" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="M4" s="26">
         <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="O4" s="27">
         <v>5</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24">
         <v>0</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="U4" s="24">
         <v>0</v>
       </c>
-      <c r="R4" s="24">
+      <c r="V4" s="24">
         <v>0</v>
       </c>
-      <c r="S4" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T4" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U4" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24" t="s">
+      <c r="W4" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X4" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y4" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>216</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M5" s="26">
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O5" s="29">
         <v>4.9</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14">
         <v>0</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="U5" s="14">
         <v>0</v>
       </c>
-      <c r="R5" s="14">
+      <c r="V5" s="14">
         <v>0</v>
       </c>
-      <c r="S5" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U5" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14" t="s">
+      <c r="W5" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X5" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y5" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="M6" s="26">
         <v>1</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="O6" s="27">
         <v>4.8</v>
       </c>
-      <c r="P6" s="24">
+      <c r="P6" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24">
         <v>0</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="U6" s="24">
         <v>0</v>
       </c>
-      <c r="R6" s="24">
+      <c r="V6" s="24">
         <v>0</v>
       </c>
-      <c r="S6" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T6" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U6" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24" t="s">
+      <c r="W6" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X6" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y6" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M7" s="26">
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="O7" s="29">
         <v>4.8</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14">
         <v>0</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="U7" s="14">
         <v>0</v>
       </c>
-      <c r="R7" s="14">
+      <c r="V7" s="14">
         <v>0</v>
       </c>
-      <c r="S7" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T7" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U7" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W7" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="X7" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y7" s="14"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W7" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X7" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y7" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z7" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA7" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="M8" s="26">
         <v>1</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="O8" s="27">
         <v>4.7</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24">
         <v>0</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="U8" s="24">
         <v>0</v>
       </c>
-      <c r="R8" s="24">
+      <c r="V8" s="24">
         <v>0</v>
       </c>
-      <c r="S8" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T8" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U8" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W8" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X8" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y8" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M9" s="26">
         <v>1</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="O9" s="29">
         <v>4.6</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14">
         <v>0</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="U9" s="14">
         <v>0</v>
       </c>
-      <c r="R9" s="14">
+      <c r="V9" s="14">
         <v>0</v>
       </c>
-      <c r="S9" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T9" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U9" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="X9" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="Y9" s="14"/>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W9" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X9" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y9" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AC9" s="14"/>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>216</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="M10" s="26">
         <v>1</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="O10" s="27">
         <v>4.5</v>
       </c>
-      <c r="P10" s="24">
+      <c r="P10" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24">
         <v>0</v>
       </c>
-      <c r="Q10" s="24">
+      <c r="U10" s="24">
         <v>0</v>
       </c>
-      <c r="R10" s="24">
+      <c r="V10" s="24">
         <v>0</v>
       </c>
-      <c r="S10" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T10" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U10" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24" t="s">
+      <c r="W10" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X10" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y10" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>216</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="M11" s="26">
         <v>1</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="O11" s="29">
         <v>4.5</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14">
         <v>0</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="U11" s="14">
         <v>0</v>
       </c>
-      <c r="R11" s="14">
+      <c r="V11" s="14">
         <v>0</v>
       </c>
-      <c r="S11" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T11" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U11" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14" t="s">
+      <c r="W11" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X11" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y11" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>216</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M12" s="26">
         <v>1</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="O12" s="27">
         <v>4.4</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24">
         <v>0</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="U12" s="24">
         <v>0</v>
       </c>
-      <c r="R12" s="24">
+      <c r="V12" s="24">
         <v>0</v>
       </c>
-      <c r="S12" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T12" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U12" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24" t="s">
+      <c r="W12" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X12" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y12" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M13" s="26">
         <v>1</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="O13" s="29">
         <v>4.4</v>
       </c>
-      <c r="P13" s="14">
+      <c r="P13" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14">
         <v>0</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="U13" s="14">
         <v>0</v>
       </c>
-      <c r="R13" s="14">
+      <c r="V13" s="14">
         <v>0</v>
       </c>
-      <c r="S13" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="T13" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="U13" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="X13" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="Y13" s="14"/>
-    </row>
-    <row r="14" ht="34" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W13" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="X13" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y13" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB13" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AC13" s="14"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M14" s="26">
         <v>1</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O14" s="27">
         <v>3.5</v>
       </c>
-      <c r="P14" s="24">
+      <c r="P14" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24">
         <v>0</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="U14" s="24">
         <v>0</v>
       </c>
-      <c r="R14" s="24">
+      <c r="V14" s="24">
         <v>0</v>
       </c>
-      <c r="S14" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="T14" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="U14" s="28"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="X14" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="Y14" s="24"/>
+      <c r="W14" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="X14" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB14" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="AC14" s="24"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y14"/>
+  <autoFilter ref="A3:AC14"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A2:AC2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" sqref="C10:C14">
@@ -7184,16 +7755,16 @@
     <dataValidation type="list" sqref="C4:C14">
       <formula1>"待核实,部分核实,已核实,团队诉求"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="S10:S14">
+    <dataValidation type="list" sqref="W10:W14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="S4:S14">
+    <dataValidation type="list" sqref="W4:W14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T10:T14">
+    <dataValidation type="list" sqref="X10:X14">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T4:T14">
+    <dataValidation type="list" sqref="X4:X14">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7230,7 +7801,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -7253,7 +7824,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -7279,22 +7850,22 @@
         <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>224</v>
@@ -7303,31 +7874,31 @@
         <v>225</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="O3" s="21" t="s">
         <v>234</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="S3" s="21" t="s">
         <v>73</v>
@@ -7335,246 +7906,246 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M4" s="24">
         <v>1</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M5" s="14">
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>403</v>
-      </c>
       <c r="K6" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M6" s="24">
         <v>1</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="24" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>118</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>118</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M7" s="14">
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q7" s="14" t="s">
         <v>417</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>412</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>128</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="G8" s="24" t="s">
         <v>128</v>
@@ -7583,55 +8154,55 @@
         <v>216</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M8" s="24">
         <v>1</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R8" s="24"/>
       <c r="S8" s="24" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>143</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>143</v>
@@ -7640,55 +8211,55 @@
         <v>216</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M9" s="14">
         <v>1</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="14" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>102</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>102</v>
@@ -7697,55 +8268,55 @@
         <v>216</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M10" s="24">
         <v>1</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="24" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>165</v>
@@ -7754,145 +8325,145 @@
         <v>216</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M11" s="14">
         <v>1</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="14" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="24" t="s">
         <v>87</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M12" s="24">
         <v>1</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="R12" s="24"/>
       <c r="S12" s="24" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="s">
         <v>210</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M13" s="14">
         <v>2</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="R13" s="14"/>
       <c r="S13" s="14" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -7933,7 +8504,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -7953,7 +8524,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -7976,16 +8547,16 @@
         <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>224</v>
@@ -7994,491 +8565,491 @@
         <v>225</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>234</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J4" s="24">
         <v>1</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J5" s="14">
         <v>1</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J6" s="24">
         <v>1</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="N6" s="24"/>
       <c r="O6" s="24" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J7" s="14">
         <v>1</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14" t="s">
         <v>118</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24" t="s">
         <v>216</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J8" s="24">
         <v>1</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N8" s="24"/>
       <c r="O8" s="24" t="s">
         <v>128</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
         <v>216</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J9" s="14">
         <v>1</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14" t="s">
         <v>143</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24" t="s">
         <v>216</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J10" s="24">
         <v>1</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="N10" s="24"/>
       <c r="O10" s="24" t="s">
         <v>102</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
         <v>216</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J11" s="14">
         <v>1</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14" t="s">
         <v>165</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J12" s="24">
         <v>1</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>210</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J13" s="14">
         <v>2</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
       <c r="P13" s="14" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -8496,6 +9067,484 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="2F62FF"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="34" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="I4" s="24">
+        <v>805</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>503</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="I6" s="24">
+        <v>4.9</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>506</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>530</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L韩国济州岛出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8520,7 +9569,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -8541,7 +9590,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>465</v>
+        <v>538</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -8565,7 +9614,7 @@
         <v>178</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>466</v>
+        <v>539</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>224</v>
@@ -8574,253 +9623,253 @@
         <v>225</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>467</v>
+        <v>540</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>468</v>
+        <v>541</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>470</v>
+        <v>543</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>471</v>
+        <v>544</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>472</v>
+        <v>545</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>473</v>
+        <v>546</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>474</v>
+        <v>547</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>475</v>
+        <v>548</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>476</v>
+        <v>549</v>
       </c>
       <c r="J4" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="L4" s="24" t="s">
         <v>396</v>
       </c>
-      <c r="K4" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>391</v>
-      </c>
       <c r="M4" s="24" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>87</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>477</v>
+        <v>550</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>478</v>
+        <v>551</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>210</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>480</v>
+        <v>553</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>481</v>
+        <v>554</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>482</v>
+        <v>555</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>483</v>
+        <v>556</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>210</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>484</v>
+        <v>557</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>485</v>
+        <v>558</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>486</v>
+        <v>559</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -8837,7 +9886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8887,7 +9936,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>488</v>
+        <v>561</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8940,7 +9989,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>489</v>
+        <v>562</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9005,94 +10054,94 @@
         <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>492</v>
+        <v>565</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>44</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>494</v>
+        <v>567</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>38</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>496</v>
+        <v>569</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>497</v>
+        <v>570</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>498</v>
+        <v>571</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>499</v>
+        <v>572</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>500</v>
+        <v>573</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>502</v>
+        <v>575</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>503</v>
+        <v>576</v>
       </c>
       <c r="V3" s="21" t="s">
         <v>50</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="X3" s="21" t="s">
         <v>153</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>505</v>
+        <v>578</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>69</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>506</v>
+        <v>579</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>509</v>
+        <v>582</v>
       </c>
       <c r="AE3" s="21" t="s">
         <v>71</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>510</v>
+        <v>583</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>511</v>
+        <v>584</v>
       </c>
       <c r="AH3" s="23" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AI3" s="22" t="s">
         <v>233</v>
@@ -9101,43 +10150,43 @@
         <v>234</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AT3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AU3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AV3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>515</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -9154,7 +10203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9191,7 +10240,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>516</v>
+        <v>588</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9232,7 +10281,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>517</v>
+        <v>589</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9285,58 +10334,58 @@
         <v>230</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>518</v>
+        <v>590</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>520</v>
+        <v>592</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>521</v>
+        <v>593</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>522</v>
+        <v>594</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>523</v>
+        <v>595</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>524</v>
+        <v>596</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>525</v>
+        <v>597</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>526</v>
+        <v>598</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>505</v>
+        <v>578</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="S3" s="21" t="s">
         <v>71</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>510</v>
+        <v>583</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>511</v>
+        <v>584</v>
       </c>
       <c r="V3" s="23" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="W3" s="22" t="s">
         <v>233</v>
@@ -9345,43 +10394,43 @@
         <v>234</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>515</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -9398,7 +10447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9437,7 +10486,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>527</v>
+        <v>599</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9486,7 +10535,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9541,7 +10590,7 @@
         <v>226</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>529</v>
+        <v>601</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>225</v>
@@ -9550,79 +10599,79 @@
         <v>230</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>530</v>
+        <v>602</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>520</v>
+        <v>592</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>531</v>
+        <v>603</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>532</v>
+        <v>604</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>533</v>
+        <v>605</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>534</v>
+        <v>606</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>535</v>
+        <v>607</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>536</v>
+        <v>608</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>537</v>
+        <v>609</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>538</v>
+        <v>610</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>539</v>
+        <v>611</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>540</v>
+        <v>612</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>541</v>
+        <v>613</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>542</v>
+        <v>614</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>543</v>
+        <v>615</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>525</v>
+        <v>597</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>526</v>
+        <v>598</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>505</v>
+        <v>578</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>71</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>510</v>
+        <v>583</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>511</v>
+        <v>584</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AE3" s="22" t="s">
         <v>233</v>
@@ -9631,43 +10680,43 @@
         <v>234</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AJ3" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="AL3" s="21" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AS3" s="21" t="s">
-        <v>515</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -9682,271 +10731,4 @@
     <oddFooter>&amp;L韩国济州岛出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AO3"/>
-  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16" style="33" customWidth="1"/>
-    <col min="8" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="13" width="18" customWidth="1"/>
-    <col min="14" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="30" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="25" width="30" customWidth="1"/>
-    <col min="26" max="26" width="16" style="18" customWidth="1"/>
-    <col min="27" max="27" width="18" style="17" customWidth="1"/>
-    <col min="28" max="29" width="30" customWidth="1"/>
-    <col min="30" max="35" width="18" customWidth="1"/>
-    <col min="36" max="36" width="30" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="16" customWidth="1"/>
-    <col min="39" max="39" width="38" customWidth="1"/>
-    <col min="40" max="40" width="36" customWidth="1"/>
-    <col min="41" max="41" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
-      <c r="AM1" s="19"/>
-      <c r="AN1" s="19"/>
-      <c r="AO1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>545</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="20"/>
-      <c r="AO2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>490</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>520</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>549</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>501</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>505</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>526</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>508</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>510</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>511</v>
-      </c>
-      <c r="Z3" s="23" t="s">
-        <v>512</v>
-      </c>
-      <c r="AA3" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="AF3" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="AG3" s="21" t="s">
-        <v>514</v>
-      </c>
-      <c r="AH3" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="AI3" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="AK3" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="AL3" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="AM3" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="AN3" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="AO3" s="21" t="s">
-        <v>515</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:AO4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="A2:AO2"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L韩国济州岛出行共创&amp;R第 &amp;P / &amp;N 页</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>